--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Primo RPA\TestProject\Данные\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F129D0D3-3845-4671-9948-3CBD7DE475DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E404618-D6C0-41F4-B105-7222013AFAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="29040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>ExScreenshotsFolderPath</t>
   </si>
@@ -55,9 +55,6 @@
     <t>adressSite</t>
   </si>
   <si>
-    <t>https://egrul.nalog.ru/index.html</t>
-  </si>
-  <si>
     <t>Сайт налоговой из ТЗ</t>
   </si>
   <si>
@@ -65,12 +62,6 @@
   </si>
   <si>
     <t>Абсолютный путь до справочника</t>
-  </si>
-  <si>
-    <t>C:\Users\user\Documents\Primo RPA\Тестовое задание Отгрузка Евраз\Справочники.xlsx</t>
-  </si>
-  <si>
-    <t>C:\Users\user\Documents\Primo RPA\Тестовое задание Отгрузка Евраз</t>
   </si>
   <si>
     <t>resultFilePath</t>
@@ -533,62 +524,51 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B3" s="5"/>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="7"/>
+      <c r="C4" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>14</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{159B7C38-33F2-45AD-8628-BD2DC0B462D7}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Primo RPA\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E404618-D6C0-41F4-B105-7222013AFAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4FF397-EE2D-458C-AB49-6D73B2C734E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Primo RPA\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4FF397-EE2D-458C-AB49-6D73B2C734E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C816C77A-C62E-4843-90C6-658F186979AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>
@@ -551,7 +551,7 @@
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
         <v>13</v>
       </c>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\Primo RPA\TestProject\Данные\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C816C77A-C62E-4843-90C6-658F186979AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE8EB54-5BE0-4F4B-B49B-BA230891757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAE8EB54-5BE0-4F4B-B49B-BA230891757E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CFD467-B884-441E-814B-A7AAC97431D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>ExScreenshotsFolderPath</t>
   </si>
@@ -73,7 +73,16 @@
     <t>preferencesPath</t>
   </si>
   <si>
-    <t>Абсолютный путь до файла Preferences браузера Google Chrome</t>
+    <t>downloadsChromePath</t>
+  </si>
+  <si>
+    <t>C:\RPA_Downloads</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до файла Preferences браузера Google Chrome (указать, если не совпадает с инструкцией)</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до папки с загрузками браузера Chrome (можно изменить на свое)</t>
   </si>
 </sst>
 </file>
@@ -153,7 +162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -162,6 +171,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -477,12 +487,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="90.28515625" customWidth="1"/>
-    <col min="3" max="3" width="81.42578125" customWidth="1"/>
+    <col min="3" max="3" width="102" bestFit="1" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -562,7 +572,18 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
+      <c r="A7" s="6" t="s">
         <v>15</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CFD467-B884-441E-814B-A7AAC97431D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F71A335-748A-41F4-B657-FF32AEAD4239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>ExScreenshotsFolderPath</t>
   </si>
@@ -76,20 +76,17 @@
     <t>downloadsChromePath</t>
   </si>
   <si>
-    <t>C:\RPA_Downloads</t>
-  </si>
-  <si>
     <t>Абсолютный путь до файла Preferences браузера Google Chrome (указать, если не совпадает с инструкцией)</t>
   </si>
   <si>
-    <t>Абсолютный путь до папки с загрузками браузера Chrome (можно изменить на свое)</t>
+    <t>Абсолютный путь до папки с загрузками браузера Chrome (можно изменить на свое, по умолчанию "C:\RPA_Downloads")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -118,6 +115,21 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
@@ -162,16 +174,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -487,12 +509,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="90.28515625" customWidth="1"/>
-    <col min="3" max="3" width="102" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -530,61 +552,86 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:26" ht="27" customHeight="1">
+      <c r="A2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:26" ht="23.25" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:26" ht="24" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:26" ht="36" customHeight="1">
+      <c r="A5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:26" ht="46.5" customHeight="1">
+      <c r="A6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="44.25" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
-      <c r="A7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>18</v>
-      </c>
+    <row r="8" spans="1:26">
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="C16" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -639,13 +686,13 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
     </row>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F71A335-748A-41F4-B657-FF32AEAD4239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798F8956-2263-4D7C-96C0-609D8430F4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798F8956-2263-4D7C-96C0-609D8430F4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF5FF59-FE55-4669-BB82-1FF57F9C883B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>
@@ -26,13 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
-  <si>
-    <t>ExScreenshotsFolderPath</t>
-  </si>
-  <si>
-    <t>Путь для сохранения снимков экрана во время ошибок - может быть полным или относительным.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>Название</t>
   </si>
@@ -43,9 +37,6 @@
     <t>Описание</t>
   </si>
   <si>
-    <t>Ошибки</t>
-  </si>
-  <si>
     <t>mainFolder</t>
   </si>
   <si>
@@ -70,16 +61,28 @@
     <t>Абсолютный путь до папки с файлом-результата</t>
   </si>
   <si>
-    <t>preferencesPath</t>
-  </si>
-  <si>
-    <t>downloadsChromePath</t>
-  </si>
-  <si>
-    <t>Абсолютный путь до файла Preferences браузера Google Chrome (указать, если не совпадает с инструкцией)</t>
-  </si>
-  <si>
-    <t>Абсолютный путь до папки с загрузками браузера Chrome (можно изменить на свое, по умолчанию "C:\RPA_Downloads")</t>
+    <t>BusinessExPath</t>
+  </si>
+  <si>
+    <t>SystemExPath</t>
+  </si>
+  <si>
+    <t>userDataPath</t>
+  </si>
+  <si>
+    <t>pathExtension</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до каталога расположения папки с профилем (создается один раз как эталонный профиль с расширением Primo)</t>
+  </si>
+  <si>
+    <t>Абсолютный путь с расширением для Primo v3</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до каталога, где находится каталог системных ошибок</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до каталога, где находится каталог бизнес-ошибок</t>
   </si>
 </sst>
 </file>
@@ -132,7 +135,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +145,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -174,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -194,6 +203,7 @@
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -520,13 +530,13 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.75">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -554,56 +564,56 @@
     </row>
     <row r="2" spans="1:26" ht="27" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="23.25" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="24" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="36" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="75.75" customHeight="1">
+      <c r="A6" s="11" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="46.5" customHeight="1">
-      <c r="A6" s="10" t="s">
-        <v>14</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="44.25" customHeight="1">
-      <c r="A7" s="10" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="67.5" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -642,24 +652,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="91.140625" customWidth="1"/>
+    <col min="3" max="3" width="101" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18.75">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -687,13 +697,20 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>1</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/TestProject/Данные/Конфигурационный файл.xlsx
+++ b/TestProject/Данные/Конфигурационный файл.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Работа\EvrazTest\TestProject\Данные\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF5FF59-FE55-4669-BB82-1FF57F9C883B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2662A665-D8E1-4F3F-BD77-5333EC952021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="29040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Параметры" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>Название</t>
   </si>
@@ -76,13 +76,16 @@
     <t>Абсолютный путь до каталога расположения папки с профилем (создается один раз как эталонный профиль с расширением Primo)</t>
   </si>
   <si>
-    <t>Абсолютный путь с расширением для Primo v3</t>
-  </si>
-  <si>
-    <t>Абсолютный путь до каталога, где находится каталог системных ошибок</t>
-  </si>
-  <si>
-    <t>Абсолютный путь до каталога, где находится каталог бизнес-ошибок</t>
+    <t>https://egrul.nalog.ru/index.html</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до каталога бизнес-ошибок</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до каталога системных ошибок</t>
+  </si>
+  <si>
+    <t>Абсолютный путь до папки с расширением Primo v3</t>
   </si>
 </sst>
 </file>
@@ -584,7 +587,9 @@
       <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="C4" s="8" t="s">
         <v>6</v>
       </c>
@@ -613,7 +618,7 @@
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="9" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -645,8 +650,11 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <hyperlinks>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{D1C91AD1-F3F6-40E9-BDF2-AB0607F265C9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -656,8 +664,7 @@
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
-    <col min="2" max="2" width="51" customWidth="1"/>
-    <col min="3" max="3" width="101" customWidth="1"/>
+    <col min="2" max="3" width="71.7109375" customWidth="1"/>
     <col min="4" max="26" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -701,7 +708,7 @@
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -710,7 +717,7 @@
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
